--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699905</v>
+        <v>127699922</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730671</v>
+        <v>730706</v>
       </c>
       <c r="R2" t="n">
-        <v>7170937</v>
+        <v>7170653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699922</v>
+        <v>127699912</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>92813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730706</v>
+        <v>730693</v>
       </c>
       <c r="R3" t="n">
-        <v>7170653</v>
+        <v>7170733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699912</v>
+        <v>127699898</v>
       </c>
       <c r="B4" t="n">
-        <v>92813</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730693</v>
+        <v>730694</v>
       </c>
       <c r="R4" t="n">
-        <v>7170733</v>
+        <v>7170715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699898</v>
+        <v>127699905</v>
       </c>
       <c r="B5" t="n">
-        <v>91295</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730694</v>
+        <v>730671</v>
       </c>
       <c r="R5" t="n">
-        <v>7170715</v>
+        <v>7170937</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699922</v>
+        <v>127699905</v>
       </c>
       <c r="B2" t="n">
-        <v>78776</v>
+        <v>79638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730706</v>
+        <v>730671</v>
       </c>
       <c r="R2" t="n">
-        <v>7170653</v>
+        <v>7170937</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699912</v>
+        <v>127699922</v>
       </c>
       <c r="B3" t="n">
-        <v>92813</v>
+        <v>78778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730693</v>
+        <v>730706</v>
       </c>
       <c r="R3" t="n">
-        <v>7170733</v>
+        <v>7170653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127699898</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699905</v>
+        <v>127699912</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>92815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730671</v>
+        <v>730693</v>
       </c>
       <c r="R5" t="n">
-        <v>7170937</v>
+        <v>7170733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699945</v>
+        <v>127699916</v>
       </c>
       <c r="B6" t="n">
-        <v>92620</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730598</v>
+        <v>730712</v>
       </c>
       <c r="R6" t="n">
-        <v>7170903</v>
+        <v>7170767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1160,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699916</v>
+        <v>127699945</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>92622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730712</v>
+        <v>730598</v>
       </c>
       <c r="R7" t="n">
-        <v>7170767</v>
+        <v>7170903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1239,7 +1240,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>127699899</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127699915</v>
+        <v>127699942</v>
       </c>
       <c r="B10" t="n">
-        <v>78777</v>
+        <v>92622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730694</v>
+        <v>730611</v>
       </c>
       <c r="R10" t="n">
-        <v>7170664</v>
+        <v>7170872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1531,7 +1531,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1550,32 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127699942</v>
+        <v>127699915</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>78779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1585,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730611</v>
+        <v>730694</v>
       </c>
       <c r="R11" t="n">
-        <v>7170872</v>
+        <v>7170664</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1628,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,32 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127699900</v>
+        <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730694</v>
+        <v>730726</v>
       </c>
       <c r="R13" t="n">
-        <v>7170664</v>
+        <v>7170759</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127699944</v>
+        <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730726</v>
+        <v>730694</v>
       </c>
       <c r="R14" t="n">
-        <v>7170759</v>
+        <v>7170664</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>127699897</v>
       </c>
       <c r="B16" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>127699933</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>127699907</v>
       </c>
       <c r="B18" t="n">
-        <v>92624</v>
+        <v>92626</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90714</v>
+        <v>90716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,32 +3005,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127699939</v>
+        <v>127699943</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730708</v>
+        <v>730694</v>
       </c>
       <c r="R26" t="n">
-        <v>7170940</v>
+        <v>7170715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3102,32 +3102,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699943</v>
+        <v>127699914</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>92815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730694</v>
+        <v>730716</v>
       </c>
       <c r="R27" t="n">
-        <v>7170715</v>
+        <v>7170782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699914</v>
+        <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>92813</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730716</v>
+        <v>730708</v>
       </c>
       <c r="R28" t="n">
-        <v>7170782</v>
+        <v>7170940</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699916</v>
+        <v>127699899</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730712</v>
+        <v>730638</v>
       </c>
       <c r="R6" t="n">
-        <v>7170767</v>
+        <v>7170784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1142,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127699899</v>
+        <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1269,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730638</v>
+        <v>730712</v>
       </c>
       <c r="R8" t="n">
-        <v>7170784</v>
+        <v>7170767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,6 +1336,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -1744,32 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127699944</v>
+        <v>127699900</v>
       </c>
       <c r="B13" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730726</v>
+        <v>730694</v>
       </c>
       <c r="R13" t="n">
-        <v>7170759</v>
+        <v>7170664</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127699900</v>
+        <v>127699944</v>
       </c>
       <c r="B14" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730694</v>
+        <v>730726</v>
       </c>
       <c r="R14" t="n">
-        <v>7170664</v>
+        <v>7170759</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699905</v>
+        <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>79638</v>
+        <v>92815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730671</v>
+        <v>730693</v>
       </c>
       <c r="R2" t="n">
-        <v>7170937</v>
+        <v>7170733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699922</v>
+        <v>127699898</v>
       </c>
       <c r="B3" t="n">
-        <v>78778</v>
+        <v>91297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730706</v>
+        <v>730694</v>
       </c>
       <c r="R3" t="n">
-        <v>7170653</v>
+        <v>7170715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699898</v>
+        <v>127699905</v>
       </c>
       <c r="B4" t="n">
-        <v>91297</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730694</v>
+        <v>730671</v>
       </c>
       <c r="R4" t="n">
-        <v>7170715</v>
+        <v>7170937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699912</v>
+        <v>127699922</v>
       </c>
       <c r="B5" t="n">
-        <v>92815</v>
+        <v>78778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730693</v>
+        <v>730706</v>
       </c>
       <c r="R5" t="n">
-        <v>7170733</v>
+        <v>7170653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699945</v>
+        <v>127699916</v>
       </c>
       <c r="B7" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730598</v>
+        <v>730712</v>
       </c>
       <c r="R7" t="n">
-        <v>7170903</v>
+        <v>7170767</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1239,6 +1239,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1257,32 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127699916</v>
+        <v>127699945</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730712</v>
+        <v>730598</v>
       </c>
       <c r="R8" t="n">
-        <v>7170767</v>
+        <v>7170903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1336,7 +1337,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127699911</v>
+        <v>127699939</v>
       </c>
       <c r="B25" t="n">
-        <v>92815</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730689</v>
+        <v>730708</v>
       </c>
       <c r="R25" t="n">
-        <v>7170735</v>
+        <v>7170940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,7 +3102,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699914</v>
+        <v>127699911</v>
       </c>
       <c r="B27" t="n">
         <v>92815</v>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730716</v>
+        <v>730689</v>
       </c>
       <c r="R27" t="n">
-        <v>7170782</v>
+        <v>7170735</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699939</v>
+        <v>127699914</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>92815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730708</v>
+        <v>730716</v>
       </c>
       <c r="R28" t="n">
-        <v>7170940</v>
+        <v>7170782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127699898</v>
       </c>
       <c r="B3" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>79638</v>
+        <v>92628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R6" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699916</v>
+        <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730712</v>
+        <v>730638</v>
       </c>
       <c r="R7" t="n">
-        <v>7170767</v>
+        <v>7170784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1239,7 +1239,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1258,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127699945</v>
+        <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730598</v>
+        <v>730712</v>
       </c>
       <c r="R8" t="n">
-        <v>7170903</v>
+        <v>7170767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,6 +1336,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>127699942</v>
       </c>
       <c r="B10" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,32 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127699900</v>
+        <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>92628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730694</v>
+        <v>730726</v>
       </c>
       <c r="R13" t="n">
-        <v>7170664</v>
+        <v>7170759</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127699944</v>
+        <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730726</v>
+        <v>730694</v>
       </c>
       <c r="R14" t="n">
-        <v>7170759</v>
+        <v>7170664</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>127699897</v>
       </c>
       <c r="B16" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699933</v>
+        <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>92632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730727</v>
+        <v>730694</v>
       </c>
       <c r="R17" t="n">
-        <v>7170762</v>
+        <v>7170715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699907</v>
+        <v>127699933</v>
       </c>
       <c r="B18" t="n">
-        <v>92626</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730694</v>
+        <v>730727</v>
       </c>
       <c r="R18" t="n">
-        <v>7170715</v>
+        <v>7170762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90716</v>
+        <v>90722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127699939</v>
+        <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>92821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730708</v>
+        <v>730689</v>
       </c>
       <c r="R25" t="n">
-        <v>7170940</v>
+        <v>7170735</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
         <v>127699943</v>
       </c>
       <c r="B26" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,10 +3102,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699911</v>
+        <v>127699914</v>
       </c>
       <c r="B27" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730689</v>
+        <v>730716</v>
       </c>
       <c r="R27" t="n">
-        <v>7170735</v>
+        <v>7170782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699914</v>
+        <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>92815</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730716</v>
+        <v>730708</v>
       </c>
       <c r="R28" t="n">
-        <v>7170782</v>
+        <v>7170940</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699912</v>
+        <v>127699905</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>79641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730693</v>
+        <v>730671</v>
       </c>
       <c r="R2" t="n">
-        <v>7170733</v>
+        <v>7170937</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699898</v>
+        <v>127699922</v>
       </c>
       <c r="B3" t="n">
-        <v>91303</v>
+        <v>78781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730694</v>
+        <v>730706</v>
       </c>
       <c r="R3" t="n">
-        <v>7170715</v>
+        <v>7170653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699905</v>
+        <v>127699912</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>92824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730671</v>
+        <v>730693</v>
       </c>
       <c r="R4" t="n">
-        <v>7170937</v>
+        <v>7170733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699922</v>
+        <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>78778</v>
+        <v>91306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730706</v>
+        <v>730694</v>
       </c>
       <c r="R5" t="n">
-        <v>7170653</v>
+        <v>7170715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699945</v>
+        <v>127699899</v>
       </c>
       <c r="B6" t="n">
-        <v>92628</v>
+        <v>79641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730598</v>
+        <v>730638</v>
       </c>
       <c r="R6" t="n">
-        <v>7170903</v>
+        <v>7170784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B7" t="n">
-        <v>79638</v>
+        <v>92631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R7" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127699942</v>
       </c>
       <c r="B10" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>127699915</v>
       </c>
       <c r="B11" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,32 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127699944</v>
+        <v>127699900</v>
       </c>
       <c r="B13" t="n">
-        <v>92628</v>
+        <v>79641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730726</v>
+        <v>730694</v>
       </c>
       <c r="R13" t="n">
-        <v>7170759</v>
+        <v>7170664</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127699900</v>
+        <v>127699944</v>
       </c>
       <c r="B14" t="n">
-        <v>79638</v>
+        <v>92631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730694</v>
+        <v>730726</v>
       </c>
       <c r="R14" t="n">
-        <v>7170664</v>
+        <v>7170759</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699897</v>
+        <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>91303</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730630</v>
+        <v>730727</v>
       </c>
       <c r="R16" t="n">
-        <v>7170857</v>
+        <v>7170762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699907</v>
+        <v>127699897</v>
       </c>
       <c r="B17" t="n">
-        <v>92632</v>
+        <v>91306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730694</v>
+        <v>730630</v>
       </c>
       <c r="R17" t="n">
-        <v>7170715</v>
+        <v>7170857</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699933</v>
+        <v>127699907</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>92635</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730727</v>
+        <v>730694</v>
       </c>
       <c r="R18" t="n">
-        <v>7170762</v>
+        <v>7170715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>77998</v>
+        <v>78001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90722</v>
+        <v>90725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127699911</v>
+        <v>127699939</v>
       </c>
       <c r="B25" t="n">
-        <v>92821</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730689</v>
+        <v>730708</v>
       </c>
       <c r="R25" t="n">
-        <v>7170735</v>
+        <v>7170940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3005,32 +3005,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127699943</v>
+        <v>127699911</v>
       </c>
       <c r="B26" t="n">
-        <v>92628</v>
+        <v>92824</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730694</v>
+        <v>730689</v>
       </c>
       <c r="R26" t="n">
-        <v>7170715</v>
+        <v>7170735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,7 +3105,7 @@
         <v>127699914</v>
       </c>
       <c r="B27" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3199,32 +3199,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699939</v>
+        <v>127699943</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730708</v>
+        <v>730694</v>
       </c>
       <c r="R28" t="n">
-        <v>7170940</v>
+        <v>7170715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699905</v>
       </c>
       <c r="B2" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127699922</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127699912</v>
       </c>
       <c r="B4" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>79641</v>
+        <v>92639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R6" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699945</v>
+        <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>92631</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730598</v>
+        <v>730638</v>
       </c>
       <c r="R7" t="n">
-        <v>7170903</v>
+        <v>7170784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127699942</v>
       </c>
       <c r="B10" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>127699915</v>
       </c>
       <c r="B11" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>127699900</v>
       </c>
       <c r="B13" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127699944</v>
       </c>
       <c r="B14" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699933</v>
+        <v>127699907</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>92643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730727</v>
+        <v>730694</v>
       </c>
       <c r="R16" t="n">
-        <v>7170762</v>
+        <v>7170715</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699897</v>
+        <v>127699933</v>
       </c>
       <c r="B17" t="n">
-        <v>91306</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730630</v>
+        <v>730727</v>
       </c>
       <c r="R17" t="n">
-        <v>7170857</v>
+        <v>7170762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699907</v>
+        <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>92635</v>
+        <v>91314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730694</v>
+        <v>730630</v>
       </c>
       <c r="R18" t="n">
-        <v>7170715</v>
+        <v>7170857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78001</v>
+        <v>78007</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90725</v>
+        <v>90733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127699939</v>
+        <v>127699914</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>92832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730708</v>
+        <v>730716</v>
       </c>
       <c r="R25" t="n">
-        <v>7170940</v>
+        <v>7170782</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3005,32 +3005,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127699911</v>
+        <v>127699943</v>
       </c>
       <c r="B26" t="n">
-        <v>92824</v>
+        <v>92639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730689</v>
+        <v>730694</v>
       </c>
       <c r="R26" t="n">
-        <v>7170735</v>
+        <v>7170715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3102,10 +3102,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699914</v>
+        <v>127699911</v>
       </c>
       <c r="B27" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730716</v>
+        <v>730689</v>
       </c>
       <c r="R27" t="n">
-        <v>7170782</v>
+        <v>7170735</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3199,32 +3199,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699943</v>
+        <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730694</v>
+        <v>730708</v>
       </c>
       <c r="R28" t="n">
-        <v>7170715</v>
+        <v>7170940</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699905</v>
+        <v>127699898</v>
       </c>
       <c r="B2" t="n">
-        <v>79647</v>
+        <v>91315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730671</v>
+        <v>730694</v>
       </c>
       <c r="R2" t="n">
-        <v>7170937</v>
+        <v>7170715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699922</v>
+        <v>127699912</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730706</v>
+        <v>730693</v>
       </c>
       <c r="R3" t="n">
-        <v>7170653</v>
+        <v>7170733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699912</v>
+        <v>127699905</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730693</v>
+        <v>730671</v>
       </c>
       <c r="R4" t="n">
-        <v>7170733</v>
+        <v>7170937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699898</v>
+        <v>127699922</v>
       </c>
       <c r="B5" t="n">
-        <v>91314</v>
+        <v>78787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730694</v>
+        <v>730706</v>
       </c>
       <c r="R5" t="n">
-        <v>7170715</v>
+        <v>7170653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127699942</v>
       </c>
       <c r="B10" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,32 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127699900</v>
+        <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>92640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730694</v>
+        <v>730726</v>
       </c>
       <c r="R13" t="n">
-        <v>7170664</v>
+        <v>7170759</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127699944</v>
+        <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>92639</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730726</v>
+        <v>730694</v>
       </c>
       <c r="R14" t="n">
-        <v>7170759</v>
+        <v>7170664</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699907</v>
+        <v>127699897</v>
       </c>
       <c r="B16" t="n">
-        <v>92643</v>
+        <v>91315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730694</v>
+        <v>730630</v>
       </c>
       <c r="R16" t="n">
-        <v>7170715</v>
+        <v>7170857</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699897</v>
+        <v>127699907</v>
       </c>
       <c r="B18" t="n">
-        <v>91314</v>
+        <v>92644</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730630</v>
+        <v>730694</v>
       </c>
       <c r="R18" t="n">
-        <v>7170857</v>
+        <v>7170715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90733</v>
+        <v>90734</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127699914</v>
+        <v>127699939</v>
       </c>
       <c r="B25" t="n">
-        <v>92832</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730716</v>
+        <v>730708</v>
       </c>
       <c r="R25" t="n">
-        <v>7170782</v>
+        <v>7170940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
         <v>127699943</v>
       </c>
       <c r="B26" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>127699911</v>
       </c>
       <c r="B27" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699939</v>
+        <v>127699914</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>92833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730708</v>
+        <v>730716</v>
       </c>
       <c r="R28" t="n">
-        <v>7170940</v>
+        <v>7170782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699898</v>
+        <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>91315</v>
+        <v>92833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730694</v>
+        <v>730693</v>
       </c>
       <c r="R2" t="n">
-        <v>7170715</v>
+        <v>7170733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699912</v>
+        <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730693</v>
+        <v>730671</v>
       </c>
       <c r="R3" t="n">
-        <v>7170733</v>
+        <v>7170937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699905</v>
+        <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>78787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730671</v>
+        <v>730706</v>
       </c>
       <c r="R4" t="n">
-        <v>7170937</v>
+        <v>7170653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699922</v>
+        <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>78787</v>
+        <v>91315</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730706</v>
+        <v>730694</v>
       </c>
       <c r="R5" t="n">
-        <v>7170653</v>
+        <v>7170715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699897</v>
+        <v>127699907</v>
       </c>
       <c r="B16" t="n">
-        <v>91315</v>
+        <v>92644</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>4365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730630</v>
+        <v>730694</v>
       </c>
       <c r="R16" t="n">
-        <v>7170857</v>
+        <v>7170715</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699933</v>
+        <v>127699897</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>91315</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730727</v>
+        <v>730630</v>
       </c>
       <c r="R17" t="n">
-        <v>7170762</v>
+        <v>7170857</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699907</v>
+        <v>127699933</v>
       </c>
       <c r="B18" t="n">
-        <v>92644</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730694</v>
+        <v>730727</v>
       </c>
       <c r="R18" t="n">
-        <v>7170715</v>
+        <v>7170762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127699939</v>
+        <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>92833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730708</v>
+        <v>730689</v>
       </c>
       <c r="R25" t="n">
-        <v>7170940</v>
+        <v>7170735</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,7 +3102,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699911</v>
+        <v>127699914</v>
       </c>
       <c r="B27" t="n">
         <v>92833</v>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730689</v>
+        <v>730716</v>
       </c>
       <c r="R27" t="n">
-        <v>7170735</v>
+        <v>7170782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699914</v>
+        <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>92833</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730716</v>
+        <v>730708</v>
       </c>
       <c r="R28" t="n">
-        <v>7170782</v>
+        <v>7170940</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699905</v>
+        <v>127699898</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>91316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730671</v>
+        <v>730694</v>
       </c>
       <c r="R3" t="n">
-        <v>7170937</v>
+        <v>7170715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699922</v>
+        <v>127699905</v>
       </c>
       <c r="B4" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730706</v>
+        <v>730671</v>
       </c>
       <c r="R4" t="n">
-        <v>7170653</v>
+        <v>7170937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699898</v>
+        <v>127699922</v>
       </c>
       <c r="B5" t="n">
-        <v>91315</v>
+        <v>78787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730694</v>
+        <v>730706</v>
       </c>
       <c r="R5" t="n">
-        <v>7170715</v>
+        <v>7170653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127699942</v>
       </c>
       <c r="B10" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>127699907</v>
       </c>
       <c r="B16" t="n">
-        <v>92644</v>
+        <v>92645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699897</v>
+        <v>127699933</v>
       </c>
       <c r="B17" t="n">
-        <v>91315</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730630</v>
+        <v>730727</v>
       </c>
       <c r="R17" t="n">
-        <v>7170857</v>
+        <v>7170762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699933</v>
+        <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>91316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730727</v>
+        <v>730630</v>
       </c>
       <c r="R18" t="n">
-        <v>7170762</v>
+        <v>7170857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90734</v>
+        <v>90735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,32 +3005,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127699943</v>
+        <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>92834</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730694</v>
+        <v>730716</v>
       </c>
       <c r="R26" t="n">
-        <v>7170715</v>
+        <v>7170782</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3102,32 +3102,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699914</v>
+        <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92833</v>
+        <v>92641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730716</v>
+        <v>730694</v>
       </c>
       <c r="R27" t="n">
-        <v>7170782</v>
+        <v>7170715</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699912</v>
+        <v>127699905</v>
       </c>
       <c r="B2" t="n">
-        <v>92834</v>
+        <v>79647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730693</v>
+        <v>730671</v>
       </c>
       <c r="R2" t="n">
-        <v>7170733</v>
+        <v>7170937</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699898</v>
+        <v>127699922</v>
       </c>
       <c r="B3" t="n">
-        <v>91316</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730694</v>
+        <v>730706</v>
       </c>
       <c r="R3" t="n">
-        <v>7170715</v>
+        <v>7170653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699905</v>
+        <v>127699898</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>91317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730671</v>
+        <v>730694</v>
       </c>
       <c r="R4" t="n">
-        <v>7170937</v>
+        <v>7170715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699922</v>
+        <v>127699912</v>
       </c>
       <c r="B5" t="n">
-        <v>78787</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730706</v>
+        <v>730693</v>
       </c>
       <c r="R5" t="n">
-        <v>7170653</v>
+        <v>7170733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699945</v>
+        <v>127699899</v>
       </c>
       <c r="B6" t="n">
-        <v>92641</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730598</v>
+        <v>730638</v>
       </c>
       <c r="R6" t="n">
-        <v>7170903</v>
+        <v>7170784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699899</v>
+        <v>127699916</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>78788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730638</v>
+        <v>730712</v>
       </c>
       <c r="R7" t="n">
-        <v>7170784</v>
+        <v>7170767</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1239,6 +1239,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1257,32 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127699916</v>
+        <v>127699945</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>92642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730712</v>
+        <v>730598</v>
       </c>
       <c r="R8" t="n">
-        <v>7170767</v>
+        <v>7170903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1336,7 +1337,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127699942</v>
+        <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>92641</v>
+        <v>78788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730611</v>
+        <v>730694</v>
       </c>
       <c r="R10" t="n">
-        <v>7170872</v>
+        <v>7170664</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1531,6 +1531,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1549,32 +1550,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127699915</v>
+        <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1585,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730694</v>
+        <v>730611</v>
       </c>
       <c r="R11" t="n">
-        <v>7170664</v>
+        <v>7170872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1628,7 +1629,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1744,32 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127699944</v>
+        <v>127699900</v>
       </c>
       <c r="B13" t="n">
-        <v>92641</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730726</v>
+        <v>730694</v>
       </c>
       <c r="R13" t="n">
-        <v>7170759</v>
+        <v>7170664</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127699900</v>
+        <v>127699944</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730694</v>
+        <v>730726</v>
       </c>
       <c r="R14" t="n">
-        <v>7170664</v>
+        <v>7170759</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699907</v>
+        <v>127699897</v>
       </c>
       <c r="B16" t="n">
-        <v>92645</v>
+        <v>91317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730694</v>
+        <v>730630</v>
       </c>
       <c r="R16" t="n">
-        <v>7170715</v>
+        <v>7170857</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699897</v>
+        <v>127699907</v>
       </c>
       <c r="B18" t="n">
-        <v>91316</v>
+        <v>92646</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730630</v>
+        <v>730694</v>
       </c>
       <c r="R18" t="n">
-        <v>7170857</v>
+        <v>7170715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90735</v>
+        <v>90736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127699911</v>
+        <v>127699939</v>
       </c>
       <c r="B25" t="n">
-        <v>92834</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730689</v>
+        <v>730708</v>
       </c>
       <c r="R25" t="n">
-        <v>7170735</v>
+        <v>7170940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3005,32 +3005,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127699914</v>
+        <v>127699943</v>
       </c>
       <c r="B26" t="n">
-        <v>92834</v>
+        <v>92642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730716</v>
+        <v>730694</v>
       </c>
       <c r="R26" t="n">
-        <v>7170782</v>
+        <v>7170715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3102,32 +3102,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699943</v>
+        <v>127699911</v>
       </c>
       <c r="B27" t="n">
-        <v>92641</v>
+        <v>92835</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730694</v>
+        <v>730689</v>
       </c>
       <c r="R27" t="n">
-        <v>7170715</v>
+        <v>7170735</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699939</v>
+        <v>127699914</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730708</v>
+        <v>730716</v>
       </c>
       <c r="R28" t="n">
-        <v>7170940</v>
+        <v>7170782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699905</v>
+        <v>127699898</v>
       </c>
       <c r="B2" t="n">
-        <v>79647</v>
+        <v>91317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730671</v>
+        <v>730694</v>
       </c>
       <c r="R2" t="n">
-        <v>7170937</v>
+        <v>7170715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699922</v>
+        <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730706</v>
+        <v>730671</v>
       </c>
       <c r="R3" t="n">
-        <v>7170653</v>
+        <v>7170937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699898</v>
+        <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>91317</v>
+        <v>78787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730694</v>
+        <v>730706</v>
       </c>
       <c r="R4" t="n">
-        <v>7170715</v>
+        <v>7170653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R6" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699916</v>
+        <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730712</v>
+        <v>730638</v>
       </c>
       <c r="R7" t="n">
-        <v>7170767</v>
+        <v>7170784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1239,7 +1239,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1258,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127699945</v>
+        <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>92642</v>
+        <v>78788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730598</v>
+        <v>730712</v>
       </c>
       <c r="R8" t="n">
-        <v>7170903</v>
+        <v>7170767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,6 +1336,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127699915</v>
+        <v>127699942</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>92642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730694</v>
+        <v>730611</v>
       </c>
       <c r="R10" t="n">
-        <v>7170664</v>
+        <v>7170872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1531,7 +1531,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1550,32 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127699942</v>
+        <v>127699915</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>78788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1585,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730611</v>
+        <v>730694</v>
       </c>
       <c r="R11" t="n">
-        <v>7170872</v>
+        <v>7170664</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1628,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -3005,32 +3005,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127699943</v>
+        <v>127699911</v>
       </c>
       <c r="B26" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730694</v>
+        <v>730689</v>
       </c>
       <c r="R26" t="n">
-        <v>7170715</v>
+        <v>7170735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3102,7 +3102,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699911</v>
+        <v>127699914</v>
       </c>
       <c r="B27" t="n">
         <v>92835</v>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730689</v>
+        <v>730716</v>
       </c>
       <c r="R27" t="n">
-        <v>7170735</v>
+        <v>7170782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3199,32 +3199,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699914</v>
+        <v>127699943</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730716</v>
+        <v>730694</v>
       </c>
       <c r="R28" t="n">
-        <v>7170782</v>
+        <v>7170715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699898</v>
+        <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>91317</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730694</v>
+        <v>730693</v>
       </c>
       <c r="R2" t="n">
-        <v>7170715</v>
+        <v>7170733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699905</v>
+        <v>127699898</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>91317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730671</v>
+        <v>730694</v>
       </c>
       <c r="R3" t="n">
-        <v>7170937</v>
+        <v>7170715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699922</v>
+        <v>127699905</v>
       </c>
       <c r="B4" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730706</v>
+        <v>730671</v>
       </c>
       <c r="R4" t="n">
-        <v>7170653</v>
+        <v>7170937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699912</v>
+        <v>127699922</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>78787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730693</v>
+        <v>730706</v>
       </c>
       <c r="R5" t="n">
-        <v>7170733</v>
+        <v>7170653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699945</v>
+        <v>127699899</v>
       </c>
       <c r="B6" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730598</v>
+        <v>730638</v>
       </c>
       <c r="R6" t="n">
-        <v>7170903</v>
+        <v>7170784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R7" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699897</v>
+        <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>91317</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730630</v>
+        <v>730727</v>
       </c>
       <c r="R16" t="n">
-        <v>7170857</v>
+        <v>7170762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699933</v>
+        <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>92646</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730727</v>
+        <v>730694</v>
       </c>
       <c r="R17" t="n">
-        <v>7170762</v>
+        <v>7170715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699907</v>
+        <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>92646</v>
+        <v>91317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730694</v>
+        <v>730630</v>
       </c>
       <c r="R18" t="n">
-        <v>7170715</v>
+        <v>7170857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699912</v>
+        <v>127699898</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>91317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730693</v>
+        <v>730694</v>
       </c>
       <c r="R2" t="n">
-        <v>7170733</v>
+        <v>7170715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699898</v>
+        <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>91317</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730694</v>
+        <v>730671</v>
       </c>
       <c r="R3" t="n">
-        <v>7170715</v>
+        <v>7170937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699905</v>
+        <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>78787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730671</v>
+        <v>730706</v>
       </c>
       <c r="R4" t="n">
-        <v>7170937</v>
+        <v>7170653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699922</v>
+        <v>127699912</v>
       </c>
       <c r="B5" t="n">
-        <v>78787</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730706</v>
+        <v>730693</v>
       </c>
       <c r="R5" t="n">
-        <v>7170653</v>
+        <v>7170733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R6" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699945</v>
+        <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730598</v>
+        <v>730638</v>
       </c>
       <c r="R7" t="n">
-        <v>7170903</v>
+        <v>7170784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699933</v>
+        <v>127699897</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>91317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730727</v>
+        <v>730630</v>
       </c>
       <c r="R16" t="n">
-        <v>7170762</v>
+        <v>7170857</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699907</v>
+        <v>127699933</v>
       </c>
       <c r="B17" t="n">
-        <v>92646</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730694</v>
+        <v>730727</v>
       </c>
       <c r="R17" t="n">
-        <v>7170715</v>
+        <v>7170762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699897</v>
+        <v>127699907</v>
       </c>
       <c r="B18" t="n">
-        <v>91317</v>
+        <v>92646</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730630</v>
+        <v>730694</v>
       </c>
       <c r="R18" t="n">
-        <v>7170857</v>
+        <v>7170715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699898</v>
+        <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>91317</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730694</v>
+        <v>730693</v>
       </c>
       <c r="R2" t="n">
-        <v>7170715</v>
+        <v>7170733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699905</v>
+        <v>127699898</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>91317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730671</v>
+        <v>730694</v>
       </c>
       <c r="R3" t="n">
-        <v>7170937</v>
+        <v>7170715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699922</v>
+        <v>127699905</v>
       </c>
       <c r="B4" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730706</v>
+        <v>730671</v>
       </c>
       <c r="R4" t="n">
-        <v>7170653</v>
+        <v>7170937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699912</v>
+        <v>127699922</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>78787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730693</v>
+        <v>730706</v>
       </c>
       <c r="R5" t="n">
-        <v>7170733</v>
+        <v>7170653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699945</v>
+        <v>127699899</v>
       </c>
       <c r="B6" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730598</v>
+        <v>730638</v>
       </c>
       <c r="R6" t="n">
-        <v>7170903</v>
+        <v>7170784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R7" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699897</v>
+        <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>91317</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730630</v>
+        <v>730727</v>
       </c>
       <c r="R16" t="n">
-        <v>7170857</v>
+        <v>7170762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699933</v>
+        <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>92646</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730727</v>
+        <v>730694</v>
       </c>
       <c r="R17" t="n">
-        <v>7170762</v>
+        <v>7170715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699907</v>
+        <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>92646</v>
+        <v>91317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730694</v>
+        <v>730630</v>
       </c>
       <c r="R18" t="n">
-        <v>7170715</v>
+        <v>7170857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R6" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699945</v>
+        <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730598</v>
+        <v>730638</v>
       </c>
       <c r="R7" t="n">
-        <v>7170903</v>
+        <v>7170784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699912</v>
+        <v>127699898</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730693</v>
+        <v>730694</v>
       </c>
       <c r="R2" t="n">
-        <v>7170733</v>
+        <v>7170715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699898</v>
+        <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>91317</v>
+        <v>79650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730694</v>
+        <v>730671</v>
       </c>
       <c r="R3" t="n">
-        <v>7170715</v>
+        <v>7170937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127699905</v>
+        <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>78790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730671</v>
+        <v>730706</v>
       </c>
       <c r="R4" t="n">
-        <v>7170937</v>
+        <v>7170653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699922</v>
+        <v>127699912</v>
       </c>
       <c r="B5" t="n">
-        <v>78787</v>
+        <v>92843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730706</v>
+        <v>730693</v>
       </c>
       <c r="R5" t="n">
-        <v>7170653</v>
+        <v>7170733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699945</v>
+        <v>127699916</v>
       </c>
       <c r="B6" t="n">
-        <v>92642</v>
+        <v>78791</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730598</v>
+        <v>730712</v>
       </c>
       <c r="R6" t="n">
-        <v>7170903</v>
+        <v>7170767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1160,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>92650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R7" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127699916</v>
+        <v>127699899</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730712</v>
+        <v>730638</v>
       </c>
       <c r="R8" t="n">
-        <v>7170767</v>
+        <v>7170784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1336,7 +1337,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127699942</v>
+        <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>92642</v>
+        <v>78791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730611</v>
+        <v>730694</v>
       </c>
       <c r="R10" t="n">
-        <v>7170872</v>
+        <v>7170664</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1531,6 +1531,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1549,32 +1550,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127699915</v>
+        <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>92650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1585,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730694</v>
+        <v>730611</v>
       </c>
       <c r="R11" t="n">
-        <v>7170664</v>
+        <v>7170872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1628,7 +1629,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,32 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127699900</v>
+        <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>92650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730694</v>
+        <v>730726</v>
       </c>
       <c r="R13" t="n">
-        <v>7170664</v>
+        <v>7170759</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127699944</v>
+        <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>92642</v>
+        <v>79650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730726</v>
+        <v>730694</v>
       </c>
       <c r="R14" t="n">
-        <v>7170759</v>
+        <v>7170664</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699933</v>
+        <v>127699897</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>91325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730727</v>
+        <v>730630</v>
       </c>
       <c r="R16" t="n">
-        <v>7170762</v>
+        <v>7170857</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699907</v>
+        <v>127699933</v>
       </c>
       <c r="B17" t="n">
-        <v>92646</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730694</v>
+        <v>730727</v>
       </c>
       <c r="R17" t="n">
-        <v>7170715</v>
+        <v>7170762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699897</v>
+        <v>127699907</v>
       </c>
       <c r="B18" t="n">
-        <v>91317</v>
+        <v>92654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730630</v>
+        <v>730694</v>
       </c>
       <c r="R18" t="n">
-        <v>7170857</v>
+        <v>7170715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78007</v>
+        <v>78010</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90736</v>
+        <v>90742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127699939</v>
+        <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>92843</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730708</v>
+        <v>730689</v>
       </c>
       <c r="R25" t="n">
-        <v>7170940</v>
+        <v>7170735</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127699911</v>
+        <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730689</v>
+        <v>730716</v>
       </c>
       <c r="R26" t="n">
-        <v>7170735</v>
+        <v>7170782</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3102,10 +3102,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699914</v>
+        <v>127699939</v>
       </c>
       <c r="B27" t="n">
-        <v>92835</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3113,21 +3113,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730716</v>
+        <v>730708</v>
       </c>
       <c r="R27" t="n">
-        <v>7170782</v>
+        <v>7170940</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,7 +3202,7 @@
         <v>127699943</v>
       </c>
       <c r="B28" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699916</v>
+        <v>127699899</v>
       </c>
       <c r="B6" t="n">
-        <v>78791</v>
+        <v>79650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730712</v>
+        <v>730638</v>
       </c>
       <c r="R6" t="n">
-        <v>7170767</v>
+        <v>7170784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,7 +1142,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127699899</v>
+        <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>79650</v>
+        <v>78791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1269,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730638</v>
+        <v>730712</v>
       </c>
       <c r="R8" t="n">
-        <v>7170784</v>
+        <v>7170767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,6 +1336,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699898</v>
+        <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>92854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730694</v>
+        <v>730693</v>
       </c>
       <c r="R2" t="n">
-        <v>7170715</v>
+        <v>7170733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
         <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>78790</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699912</v>
+        <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>92843</v>
+        <v>91336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730693</v>
+        <v>730694</v>
       </c>
       <c r="R5" t="n">
-        <v>7170733</v>
+        <v>7170715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699899</v>
+        <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>79650</v>
+        <v>92661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730638</v>
+        <v>730598</v>
       </c>
       <c r="R6" t="n">
-        <v>7170784</v>
+        <v>7170903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127699945</v>
+        <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>92650</v>
+        <v>79661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730598</v>
+        <v>730638</v>
       </c>
       <c r="R7" t="n">
-        <v>7170903</v>
+        <v>7170784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>78802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>78791</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92650</v>
+        <v>92661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78790</v>
+        <v>78801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92650</v>
+        <v>92661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92843</v>
+        <v>92854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,32 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127699897</v>
+        <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>91325</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730630</v>
+        <v>730727</v>
       </c>
       <c r="R16" t="n">
-        <v>7170857</v>
+        <v>7170762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,32 +2132,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699933</v>
+        <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>92665</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730727</v>
+        <v>730694</v>
       </c>
       <c r="R17" t="n">
-        <v>7170762</v>
+        <v>7170715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,32 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699907</v>
+        <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>92654</v>
+        <v>91336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730694</v>
+        <v>730630</v>
       </c>
       <c r="R18" t="n">
-        <v>7170715</v>
+        <v>7170857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78010</v>
+        <v>78021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90742</v>
+        <v>90753</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78790</v>
+        <v>78801</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>92843</v>
+        <v>92854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>92843</v>
+        <v>92854</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,32 +3102,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699939</v>
+        <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>92661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730708</v>
+        <v>730694</v>
       </c>
       <c r="R27" t="n">
-        <v>7170940</v>
+        <v>7170715</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3199,32 +3199,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127699943</v>
+        <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>92650</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730694</v>
+        <v>730708</v>
       </c>
       <c r="R28" t="n">
-        <v>7170715</v>
+        <v>7170940</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>79661</v>
+        <v>79739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91336</v>
+        <v>91469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92661</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,14 +1172,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>79661</v>
+        <v>79739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,14 +1273,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78802</v>
+        <v>78878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,14 +1375,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79661</v>
+        <v>79739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,14 +1476,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>78878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,14 +1578,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92661</v>
+        <v>92794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,14 +1679,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,14 +1780,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92661</v>
+        <v>92794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,14 +1881,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>79661</v>
+        <v>79739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,14 +1982,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92854</v>
+        <v>92989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,14 +2083,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2128,14 +2184,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92665</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,14 +2285,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91336</v>
+        <v>91469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2322,14 +2386,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2419,14 +2487,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78021</v>
+        <v>78092</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2516,14 +2588,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2613,14 +2689,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90753</v>
+        <v>90886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2710,14 +2790,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79661</v>
+        <v>79739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,14 +2891,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2904,14 +2992,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>92854</v>
+        <v>92989</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3001,14 +3093,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>92854</v>
+        <v>92989</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3098,14 +3194,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92661</v>
+        <v>92794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,14 +3295,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3292,7 +3396,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78092</v>
+        <v>78096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90886</v>
+        <v>90890</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78096</v>
+        <v>78037</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90890</v>
+        <v>90895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90902</v>
+        <v>90905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78042</v>
+        <v>78043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90905</v>
+        <v>90908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90908</v>
+        <v>90912</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90912</v>
+        <v>90919</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78047</v>
+        <v>78049</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90919</v>
+        <v>90921</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78049</v>
+        <v>78051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699905</v>
       </c>
       <c r="B3" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699922</v>
       </c>
       <c r="B4" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699899</v>
       </c>
       <c r="B7" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699916</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>127699902</v>
       </c>
       <c r="B9" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>127699915</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>127699923</v>
       </c>
       <c r="B12" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127699900</v>
       </c>
       <c r="B14" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127699933</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127699931</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>127699948</v>
       </c>
       <c r="B20" t="n">
-        <v>78051</v>
+        <v>78052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>127699932</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>127699901</v>
       </c>
       <c r="B23" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>127699920</v>
       </c>
       <c r="B24" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>127699939</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 62308-2022 artfynd.xlsx
+++ b/artfynd/A 62308-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699912</v>
       </c>
       <c r="B2" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699898</v>
       </c>
       <c r="B5" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699945</v>
       </c>
       <c r="B6" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>127699942</v>
       </c>
       <c r="B11" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127699944</v>
       </c>
       <c r="B13" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>127699913</v>
       </c>
       <c r="B15" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>127699907</v>
       </c>
       <c r="B17" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127699897</v>
       </c>
       <c r="B18" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>127699929</v>
       </c>
       <c r="B22" t="n">
-        <v>90927</v>
+        <v>90931</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127699911</v>
       </c>
       <c r="B25" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>127699914</v>
       </c>
       <c r="B26" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>127699943</v>
       </c>
       <c r="B27" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
